--- a/public/templates/leads_import_pm_suryagarh.xlsx
+++ b/public/templates/leads_import_pm_suryagarh.xlsx
@@ -7871,6 +7871,14 @@
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A1:L1"/>
   </mergeCells>
+  <dataValidations count="2">
+    <dataValidation sqref="E5:E504" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Website,Referral,Cold Call,Email,Walk-in,Social Media,Digital Marketing,Campaign,Others"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F5:F504" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"High,Medium,Low"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
